--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49714-2025 artfynd.xlsx
+++ b/artfynd/A 49714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129260093</v>
       </c>
       <c r="B2" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
